--- a/data/trans_dic/IP31KM11_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM11_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,27; 100,0</t>
+          <t>92,91; 99,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92,58; 99,25</t>
+          <t>94,82; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95,53; 99,53</t>
+          <t>94,92; 99,44</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94,77; 100,0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>94,82; 100,0</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97,45; 100,0</t>
+          <t>96,86; 100,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,65; 99,1</t>
+          <t>92,52; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94,06; 100,0</t>
+          <t>88,76; 98,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94,53; 99,37</t>
+          <t>93,58; 99,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,08; 99,31</t>
+          <t>87,44; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,99; 100,0</t>
+          <t>91,16; 99,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,97; 98,98</t>
+          <t>92,14; 98,94</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,82; 98,83</t>
+          <t>91,61; 99,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,4; 99,44</t>
+          <t>88,65; 98,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,3; 98,73</t>
+          <t>92,51; 98,65</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94,56; 99,2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>80,14; 98,88</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,27; 99,48</t>
+          <t>96,9; 99,53</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,99; 100,0</t>
+          <t>93,33; 99,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,86; 99,03</t>
+          <t>97,6; 100,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95,06; 99,11</t>
+          <t>96,02; 99,27</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>98,12; 99,49</t>
+          <t>96,41; 98,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>93,87; 98,27</t>
+          <t>97,92; 99,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96,37; 98,66</t>
+          <t>97,41; 98,74</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70732</t>
+          <t>58635</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>54288</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143377</t>
+          <t>112924</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68020; 71400</t>
+          <t>55988; 59811</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69069; 74047</t>
+          <t>52079; 54922</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139475; 145318</t>
+          <t>109336; 114546</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>140</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>125649</t>
+          <t>113049</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>124478</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250126</t>
+          <t>212382</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108939; 114951</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>119876; 126423</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>245637; 252071</t>
+          <t>207553; 214284</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>56321</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63502</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117218</t>
+          <t>108313</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50358; 55052</t>
+          <t>53016; 57299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60796; 64633</t>
+          <t>48029; 53464</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113611; 119423</t>
+          <t>104262; 110414</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73248</t>
+          <t>68561</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140976</t>
+          <t>135654</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63467; 69200</t>
+          <t>61049; 69816</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67826; 75367</t>
+          <t>64232; 70080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134847; 143574</t>
+          <t>129249; 138795</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>45768</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95001</t>
+          <t>88222</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39782; 43773</t>
+          <t>43249; 46821</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49158; 53483</t>
+          <t>39260; 43719</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91503; 96830</t>
+          <t>84643; 90264</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>174</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>123696</t>
+          <t>137126</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>146890</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>270586</t>
+          <t>258949</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>132925; 139440</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124248; 153300</t>
-        </is>
-      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>246041; 277288</t>
+          <t>254268; 261159</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>183</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>127941</t>
+          <t>152516</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>148963</t>
+          <t>137256</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>276902</t>
+          <t>289772</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>124796; 128665</t>
+          <t>146660; 155721</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>141616; 152663</t>
+          <t>134592; 137900</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>268854; 280307</t>
+          <t>283298; 292893</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>904</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>646262</t>
+          <t>670086</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>722845</t>
+          <t>611077</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1369107</t>
+          <t>1281162</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>640876; 649796</t>
+          <t>662166; 676812</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>699061; 731853</t>
+          <t>605353; 614642</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1347114; 1379103</t>
+          <t>1271295; 1288578</t>
         </is>
       </c>
     </row>
